--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.39198286181417</v>
+        <v>5.263697215044803</v>
       </c>
       <c r="D2" t="n">
-        <v>31.67627553701476</v>
+        <v>5.1473947747649</v>
       </c>
       <c r="E2" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F2" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.99517399766613</v>
+        <v>4.711715774620745</v>
       </c>
       <c r="D3" t="n">
-        <v>28.25298056251829</v>
+        <v>4.591109341409223</v>
       </c>
       <c r="E3" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F3" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.04866622328166</v>
+        <v>5.53290826128327</v>
       </c>
       <c r="D4" t="n">
-        <v>33.40563183152226</v>
+        <v>5.428415172622368</v>
       </c>
       <c r="E4" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F4" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.85078891201301</v>
+        <v>3.550753198202114</v>
       </c>
       <c r="D5" t="n">
-        <v>21.13842344924367</v>
+        <v>3.434993810502096</v>
       </c>
       <c r="E5" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F5" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.04192083917543</v>
+        <v>2.281812136366007</v>
       </c>
       <c r="D6" t="n">
-        <v>13.35792418158927</v>
+        <v>2.170662679508256</v>
       </c>
       <c r="E6" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F6" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.57655851972078</v>
+        <v>4.968690759454627</v>
       </c>
       <c r="D7" t="n">
-        <v>30.4918775203686</v>
+        <v>4.954930097059898</v>
       </c>
       <c r="E7" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F7" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.10480622569388</v>
+        <v>5.379531011675255</v>
       </c>
       <c r="D8" t="n">
-        <v>33.25116889455067</v>
+        <v>5.403314945364484</v>
       </c>
       <c r="E8" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F8" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.74354811279131</v>
+        <v>5.483326568328588</v>
       </c>
       <c r="D9" t="n">
-        <v>34.22000613216426</v>
+        <v>5.560750996476692</v>
       </c>
       <c r="E9" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F9" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.29099946286622</v>
+        <v>4.434787412715762</v>
       </c>
       <c r="D10" t="n">
-        <v>28.03813190575953</v>
+        <v>4.556196434685924</v>
       </c>
       <c r="E10" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F10" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.78686666305025</v>
+        <v>5.815365832745665</v>
       </c>
       <c r="D11" t="n">
-        <v>36.43441193625952</v>
+        <v>5.920591939642173</v>
       </c>
       <c r="E11" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F11" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.88224183220041</v>
+        <v>4.693364297732566</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8492014262124</v>
+        <v>4.687995231759515</v>
       </c>
       <c r="E12" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F12" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.547950662164123</v>
+        <v>0.90154198260167</v>
       </c>
       <c r="D13" t="n">
-        <v>5.579053328015546</v>
+        <v>0.9065961658025263</v>
       </c>
       <c r="E13" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F13" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.91789227694306</v>
+        <v>5.349157495003247</v>
       </c>
       <c r="D14" t="n">
-        <v>32.9213288578563</v>
+        <v>5.349715939401648</v>
       </c>
       <c r="E14" t="n">
-        <v>8.519669628862971</v>
+        <v>1.384446314690232</v>
       </c>
       <c r="F14" t="n">
-        <v>8.648653876616272</v>
+        <v>1.405406254950144</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
